--- a/manuals/Menu hiearchy.xlsx
+++ b/manuals/Menu hiearchy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schaeffler-my.sharepoint.com/personal/uiv10467_vitesco_com/Documents/Plocha/AETS/AETS/SW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schaeffler-my.sharepoint.com/personal/uiv10467_vitesco_com/Documents/Plocha/AETS/AETS/manuals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{811DFCE9-6A9A-453A-A123-52D0C47C4857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30712972-3AF0-41F7-A6A5-BBD11EB30A21}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{811DFCE9-6A9A-453A-A123-52D0C47C4857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96A6F5EE-2DD4-49A7-946B-2EC40BABA3A7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E6C8F8F3-ACBD-40E2-94DA-A7435C16BF12}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2064" uniqueCount="92">
   <si>
     <t>A</t>
   </si>
@@ -308,6 +308,12 @@
   <si>
     <t>Set Count BOT</t>
   </si>
+  <si>
+    <t xml:space="preserve">Calibration 2 </t>
+  </si>
+  <si>
+    <t>Calibration 1</t>
+  </si>
 </sst>
 </file>
 
@@ -439,6 +445,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -455,24 +479,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,16 +501,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>86591</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>173181</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>15153</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>199161</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>432955</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>103909</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>380999</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -518,9 +524,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="14633864" y="8139545"/>
-          <a:ext cx="1558636" cy="346364"/>
+        <a:xfrm>
+          <a:off x="7444653" y="20773161"/>
+          <a:ext cx="8659" cy="1205776"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2060,6 +2066,59 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1BE5F6F-31BA-44DA-9626-3663153727BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="15692438" y="23931562"/>
+          <a:ext cx="1095374" cy="1"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="152400">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2391,10 +2450,10 @@
   <sheetData>
     <row r="3" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="4"/>
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2435,8 +2494,8 @@
       <c r="X4" s="1"/>
     </row>
     <row r="5" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
       <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2479,8 +2538,8 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2517,8 +2576,8 @@
       <c r="X6" s="1"/>
     </row>
     <row r="7" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
       <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2562,10 +2621,10 @@
     </row>
     <row r="8" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="4"/>
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
@@ -2608,8 +2667,8 @@
       <c r="X9" s="1"/>
     </row>
     <row r="10" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -2644,8 +2703,8 @@
       <c r="X10" s="1"/>
     </row>
     <row r="11" spans="2:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
@@ -2682,8 +2741,8 @@
       <c r="X11" s="1"/>
     </row>
     <row r="12" spans="2:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
@@ -2721,10 +2780,10 @@
     </row>
     <row r="13" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="4"/>
       <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
@@ -2773,8 +2832,8 @@
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
@@ -2813,8 +2872,8 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
@@ -2853,8 +2912,8 @@
       <c r="X16" s="1"/>
     </row>
     <row r="17" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
@@ -2886,10 +2945,10 @@
     </row>
     <row r="26" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="4"/>
       <c r="E27" s="1" t="s">
         <v>32</v>
       </c>
@@ -2926,10 +2985,10 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Z27" s="9" t="s">
+      <c r="Z27" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AA27" s="10"/>
+      <c r="AA27" s="4"/>
       <c r="AC27" s="1" t="s">
         <v>32</v>
       </c>
@@ -2968,8 +3027,8 @@
       <c r="AV27" s="1"/>
     </row>
     <row r="28" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
@@ -3020,8 +3079,8 @@
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="12"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="6"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1" t="s">
@@ -3058,8 +3117,8 @@
       <c r="AV28" s="1"/>
     </row>
     <row r="29" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
@@ -3096,8 +3155,8 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="12"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="6"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1" t="s">
@@ -3134,8 +3193,8 @@
       <c r="AV29" s="1"/>
     </row>
     <row r="30" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
@@ -3172,8 +3231,8 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Z30" s="13"/>
-      <c r="AA30" s="14"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="8"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
@@ -3197,10 +3256,10 @@
     </row>
     <row r="31" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="4"/>
       <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3239,10 +3298,10 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Z32" s="9" t="s">
+      <c r="Z32" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AA32" s="10"/>
+      <c r="AA32" s="4"/>
       <c r="AC32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3281,8 +3340,8 @@
       <c r="AV32" s="1"/>
     </row>
     <row r="33" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
@@ -3319,8 +3378,8 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="12"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="6"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1" t="s">
@@ -3361,8 +3420,8 @@
       <c r="AV33" s="1"/>
     </row>
     <row r="34" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
@@ -3399,8 +3458,8 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="12"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="6"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1" t="s">
@@ -3451,8 +3510,8 @@
       <c r="AV34" s="1"/>
     </row>
     <row r="35" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -3489,8 +3548,8 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="14"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="8"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1" t="s">
@@ -3532,10 +3591,10 @@
     </row>
     <row r="36" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z37" s="9" t="s">
+      <c r="Z37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA37" s="10"/>
+      <c r="AA37" s="4"/>
       <c r="AC37" s="1" t="s">
         <v>32</v>
       </c>
@@ -3580,8 +3639,8 @@
       <c r="AV37" s="1"/>
     </row>
     <row r="38" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z38" s="11"/>
-      <c r="AA38" s="12"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="6"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1" t="s">
@@ -3624,8 +3683,8 @@
       <c r="AV38" s="1"/>
     </row>
     <row r="39" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="Z39" s="11"/>
-      <c r="AA39" s="12"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="6"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
@@ -3648,8 +3707,8 @@
       <c r="AV39" s="1"/>
     </row>
     <row r="40" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z40" s="13"/>
-      <c r="AA40" s="14"/>
+      <c r="Z40" s="7"/>
+      <c r="AA40" s="8"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
@@ -3673,10 +3732,10 @@
     </row>
     <row r="41" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="10"/>
+      <c r="C42" s="4"/>
       <c r="E42" s="1" t="s">
         <v>32</v>
       </c>
@@ -3715,8 +3774,8 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
@@ -3753,10 +3812,10 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Z43" s="9" t="s">
+      <c r="Z43" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AA43" s="10"/>
+      <c r="AA43" s="4"/>
       <c r="AC43" s="1" t="s">
         <v>32</v>
       </c>
@@ -3795,8 +3854,8 @@
       <c r="AV43" s="1"/>
     </row>
     <row r="44" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
@@ -3839,8 +3898,8 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Z44" s="11"/>
-      <c r="AA44" s="12"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="6"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1" t="s">
@@ -3881,8 +3940,8 @@
       <c r="AV44" s="1"/>
     </row>
     <row r="45" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="8"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -3903,8 +3962,8 @@
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="12"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="6"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1" t="s">
@@ -3945,8 +4004,8 @@
       <c r="AV45" s="1"/>
     </row>
     <row r="46" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z46" s="13"/>
-      <c r="AA46" s="14"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="8"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
@@ -3969,10 +4028,10 @@
       <c r="AV46" s="1"/>
     </row>
     <row r="47" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="4"/>
       <c r="E47" s="1" t="s">
         <v>32</v>
       </c>
@@ -4011,8 +4070,8 @@
       <c r="X47" s="1"/>
     </row>
     <row r="48" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
@@ -4047,8 +4106,8 @@
       <c r="X48" s="1"/>
     </row>
     <row r="49" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
@@ -4081,10 +4140,10 @@
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Z49" s="9" t="s">
+      <c r="Z49" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AA49" s="10"/>
+      <c r="AA49" s="4"/>
       <c r="AC49" s="1" t="s">
         <v>32</v>
       </c>
@@ -4123,8 +4182,8 @@
       <c r="AV49" s="1"/>
     </row>
     <row r="50" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="13"/>
-      <c r="C50" s="14"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="8"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
@@ -4157,8 +4216,8 @@
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Z50" s="11"/>
-      <c r="AA50" s="12"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="6"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1" t="s">
@@ -4207,8 +4266,8 @@
       <c r="AV50" s="1"/>
     </row>
     <row r="51" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z51" s="11"/>
-      <c r="AA51" s="12"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="6"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1" t="s">
@@ -4255,10 +4314,10 @@
       <c r="AV51" s="1"/>
     </row>
     <row r="52" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="4"/>
       <c r="E52" s="1" t="s">
         <v>32</v>
       </c>
@@ -4293,8 +4352,8 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Z52" s="13"/>
-      <c r="AA52" s="14"/>
+      <c r="Z52" s="7"/>
+      <c r="AA52" s="8"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1" t="s">
@@ -4341,8 +4400,8 @@
       <c r="AV52" s="1"/>
     </row>
     <row r="53" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B53" s="11"/>
-      <c r="C53" s="12"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -4365,8 +4424,8 @@
       <c r="X53" s="1"/>
     </row>
     <row r="54" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -4389,8 +4448,8 @@
       <c r="X54" s="1"/>
     </row>
     <row r="55" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="13"/>
-      <c r="C55" s="14"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -4414,10 +4473,10 @@
     </row>
     <row r="56" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="4"/>
       <c r="E57" s="1" t="s">
         <v>32</v>
       </c>
@@ -4454,10 +4513,10 @@
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
-      <c r="Z57" s="9" t="s">
+      <c r="Z57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AA57" s="10"/>
+      <c r="AA57" s="4"/>
       <c r="AC57" s="1" t="s">
         <v>32</v>
       </c>
@@ -4496,8 +4555,8 @@
       <c r="AV57" s="1"/>
     </row>
     <row r="58" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
@@ -4536,8 +4595,8 @@
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
-      <c r="Z58" s="11"/>
-      <c r="AA58" s="12"/>
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="6"/>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1" t="s">
@@ -4576,8 +4635,8 @@
       <c r="AV58" s="1"/>
     </row>
     <row r="59" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
@@ -4616,8 +4675,8 @@
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
-      <c r="Z59" s="11"/>
-      <c r="AA59" s="12"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="6"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1" t="s">
@@ -4656,8 +4715,8 @@
       <c r="AV59" s="1"/>
     </row>
     <row r="60" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="13"/>
-      <c r="C60" s="14"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
@@ -4698,8 +4757,8 @@
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
-      <c r="Z60" s="13"/>
-      <c r="AA60" s="14"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="8"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1" t="s">
@@ -4739,10 +4798,10 @@
     </row>
     <row r="61" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="4"/>
       <c r="E62" s="1" t="s">
         <v>32</v>
       </c>
@@ -4779,10 +4838,10 @@
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
-      <c r="Z62" s="9" t="s">
+      <c r="Z62" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AA62" s="10"/>
+      <c r="AA62" s="4"/>
       <c r="AC62" s="1" t="s">
         <v>32</v>
       </c>
@@ -4823,8 +4882,8 @@
       <c r="AV62" s="1"/>
     </row>
     <row r="63" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
@@ -4871,8 +4930,8 @@
       </c>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
-      <c r="Z63" s="11"/>
-      <c r="AA63" s="12"/>
+      <c r="Z63" s="5"/>
+      <c r="AA63" s="6"/>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1" t="s">
@@ -4911,8 +4970,8 @@
       <c r="AV63" s="1"/>
     </row>
     <row r="64" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
@@ -4957,8 +5016,8 @@
       </c>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
-      <c r="Z64" s="11"/>
-      <c r="AA64" s="12"/>
+      <c r="Z64" s="5"/>
+      <c r="AA64" s="6"/>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
       <c r="AE64" s="1" t="s">
@@ -4997,8 +5056,8 @@
       <c r="AV64" s="1"/>
     </row>
     <row r="65" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="13"/>
-      <c r="C65" s="14"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -5019,8 +5078,8 @@
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
-      <c r="Z65" s="13"/>
-      <c r="AA65" s="14"/>
+      <c r="Z65" s="7"/>
+      <c r="AA65" s="8"/>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
@@ -5044,10 +5103,10 @@
     </row>
     <row r="67" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="4"/>
       <c r="E68" s="1" t="s">
         <v>32</v>
       </c>
@@ -5086,8 +5145,8 @@
       <c r="X68" s="1"/>
     </row>
     <row r="69" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
@@ -5136,10 +5195,10 @@
       </c>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
-      <c r="Z69" s="9" t="s">
+      <c r="Z69" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AA69" s="10"/>
+      <c r="AA69" s="4"/>
       <c r="AC69" s="1" t="s">
         <v>32</v>
       </c>
@@ -5178,8 +5237,8 @@
       <c r="AV69" s="1"/>
     </row>
     <row r="70" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B70" s="11"/>
-      <c r="C70" s="12"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
@@ -5228,8 +5287,8 @@
       </c>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
-      <c r="Z70" s="11"/>
-      <c r="AA70" s="12"/>
+      <c r="Z70" s="5"/>
+      <c r="AA70" s="6"/>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
       <c r="AE70" s="1" t="s">
@@ -5278,8 +5337,8 @@
       <c r="AV70" s="1"/>
     </row>
     <row r="71" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="13"/>
-      <c r="C71" s="14"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="8"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1" t="s">
@@ -5328,8 +5387,8 @@
       </c>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
-      <c r="Z71" s="11"/>
-      <c r="AA71" s="12"/>
+      <c r="Z71" s="5"/>
+      <c r="AA71" s="6"/>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
       <c r="AE71" s="1" t="s">
@@ -5382,8 +5441,8 @@
       <c r="AV71" s="1"/>
     </row>
     <row r="72" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z72" s="13"/>
-      <c r="AA72" s="14"/>
+      <c r="Z72" s="7"/>
+      <c r="AA72" s="8"/>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
       <c r="AE72" s="1"/>
@@ -5406,10 +5465,10 @@
       <c r="AV72" s="1"/>
     </row>
     <row r="73" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="4"/>
       <c r="E73" s="1" t="s">
         <v>32</v>
       </c>
@@ -5462,8 +5521,8 @@
       <c r="X73" s="1"/>
     </row>
     <row r="74" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B74" s="11"/>
-      <c r="C74" s="12"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -5484,10 +5543,10 @@
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
-      <c r="Z74" s="9" t="s">
+      <c r="Z74" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AA74" s="10"/>
+      <c r="AA74" s="4"/>
       <c r="AC74" s="1" t="s">
         <v>32</v>
       </c>
@@ -5526,8 +5585,8 @@
       <c r="AV74" s="1"/>
     </row>
     <row r="75" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="11"/>
-      <c r="C75" s="12"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="6"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -5548,8 +5607,8 @@
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
-      <c r="Z75" s="11"/>
-      <c r="AA75" s="12"/>
+      <c r="Z75" s="5"/>
+      <c r="AA75" s="6"/>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
       <c r="AE75" s="1" t="s">
@@ -5590,8 +5649,8 @@
       <c r="AV75" s="1"/>
     </row>
     <row r="76" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="13"/>
-      <c r="C76" s="14"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="8"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -5612,8 +5671,8 @@
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
-      <c r="Z76" s="11"/>
-      <c r="AA76" s="12"/>
+      <c r="Z76" s="5"/>
+      <c r="AA76" s="6"/>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
       <c r="AE76" s="1"/>
@@ -5636,8 +5695,8 @@
       <c r="AV76" s="1"/>
     </row>
     <row r="77" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z77" s="13"/>
-      <c r="AA77" s="14"/>
+      <c r="Z77" s="7"/>
+      <c r="AA77" s="8"/>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
       <c r="AE77" s="1"/>
@@ -5661,10 +5720,10 @@
     </row>
     <row r="78" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="79" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Z79" s="9" t="s">
+      <c r="Z79" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AA79" s="10"/>
+      <c r="AA79" s="4"/>
       <c r="AC79" s="1" t="s">
         <v>32</v>
       </c>
@@ -5703,10 +5762,10 @@
       <c r="AV79" s="1"/>
     </row>
     <row r="80" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="4"/>
       <c r="E80" s="1" t="s">
         <v>32</v>
       </c>
@@ -5745,8 +5804,8 @@
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
-      <c r="Z80" s="11"/>
-      <c r="AA80" s="12"/>
+      <c r="Z80" s="5"/>
+      <c r="AA80" s="6"/>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
       <c r="AE80" s="1" t="s">
@@ -5803,8 +5862,8 @@
       </c>
     </row>
     <row r="81" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B81" s="11"/>
-      <c r="C81" s="12"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="6"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
@@ -5845,8 +5904,8 @@
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
-      <c r="Z81" s="11"/>
-      <c r="AA81" s="12"/>
+      <c r="Z81" s="5"/>
+      <c r="AA81" s="6"/>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
       <c r="AE81" s="1" t="s">
@@ -5895,8 +5954,8 @@
       <c r="AV81" s="1"/>
     </row>
     <row r="82" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="11"/>
-      <c r="C82" s="12"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
@@ -5937,8 +5996,8 @@
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
-      <c r="Z82" s="13"/>
-      <c r="AA82" s="14"/>
+      <c r="Z82" s="7"/>
+      <c r="AA82" s="8"/>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
       <c r="AE82" s="1" t="s">
@@ -5983,8 +6042,8 @@
       <c r="AV82" s="1"/>
     </row>
     <row r="83" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="13"/>
-      <c r="C83" s="14"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="8"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
@@ -6028,10 +6087,10 @@
     </row>
     <row r="85" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="86" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C86" s="10"/>
+      <c r="C86" s="4"/>
       <c r="E86" s="1" t="s">
         <v>32</v>
       </c>
@@ -6076,10 +6135,10 @@
       </c>
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
-      <c r="Z86" s="9" t="s">
+      <c r="Z86" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AA86" s="10"/>
+      <c r="AA86" s="4"/>
       <c r="AC86" s="1" t="s">
         <v>32</v>
       </c>
@@ -6132,8 +6191,8 @@
       <c r="AV86" s="1"/>
     </row>
     <row r="87" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B87" s="11"/>
-      <c r="C87" s="12"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
@@ -6174,8 +6233,8 @@
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
-      <c r="Z87" s="11"/>
-      <c r="AA87" s="12"/>
+      <c r="Z87" s="5"/>
+      <c r="AA87" s="6"/>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
       <c r="AE87" s="1" t="s">
@@ -6228,8 +6287,8 @@
       <c r="AV87" s="1"/>
     </row>
     <row r="88" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B88" s="11"/>
-      <c r="C88" s="12"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="6"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
@@ -6272,8 +6331,8 @@
       </c>
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
-      <c r="Z88" s="11"/>
-      <c r="AA88" s="12"/>
+      <c r="Z88" s="5"/>
+      <c r="AA88" s="6"/>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
       <c r="AE88" s="1"/>
@@ -6296,8 +6355,8 @@
       <c r="AV88" s="1"/>
     </row>
     <row r="89" spans="2:48" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="13"/>
-      <c r="C89" s="14"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="8"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
@@ -6338,8 +6397,8 @@
       </c>
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
-      <c r="Z89" s="13"/>
-      <c r="AA89" s="14"/>
+      <c r="Z89" s="7"/>
+      <c r="AA89" s="8"/>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
       <c r="AE89" s="1"/>
@@ -6363,10 +6422,10 @@
     </row>
     <row r="95" spans="2:48" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="2:48" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="4"/>
       <c r="E96" s="1" t="s">
         <v>32</v>
       </c>
@@ -6417,8 +6476,8 @@
       <c r="X96" s="1"/>
     </row>
     <row r="97" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B97" s="11"/>
-      <c r="C97" s="12"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1" t="s">
@@ -6463,8 +6522,8 @@
       <c r="X97" s="1"/>
     </row>
     <row r="98" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B98" s="11"/>
-      <c r="C98" s="12"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="6"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
@@ -6487,8 +6546,8 @@
       <c r="X98" s="1"/>
     </row>
     <row r="99" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="13"/>
-      <c r="C99" s="14"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="8"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -6512,10 +6571,10 @@
     </row>
     <row r="101" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="102" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C102" s="4"/>
+      <c r="C102" s="10"/>
       <c r="E102" s="1" t="s">
         <v>32</v>
       </c>
@@ -6566,8 +6625,8 @@
       <c r="X102" s="1"/>
     </row>
     <row r="103" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B103" s="5"/>
-      <c r="C103" s="6"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="12"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1" t="s">
@@ -6616,8 +6675,8 @@
       <c r="X103" s="1"/>
     </row>
     <row r="104" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B104" s="5"/>
-      <c r="C104" s="6"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="12"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
@@ -6662,8 +6721,8 @@
       <c r="X104" s="1"/>
     </row>
     <row r="105" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="7"/>
-      <c r="C105" s="8"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="14"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
@@ -6687,10 +6746,10 @@
     </row>
     <row r="107" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C108" s="4"/>
+      <c r="C108" s="10"/>
       <c r="E108" s="1" t="s">
         <v>32</v>
       </c>
@@ -6741,8 +6800,8 @@
       <c r="X108" s="1"/>
     </row>
     <row r="109" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B109" s="5"/>
-      <c r="C109" s="6"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="12"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1" t="s">
@@ -6783,8 +6842,8 @@
       <c r="X109" s="1"/>
     </row>
     <row r="110" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B110" s="5"/>
-      <c r="C110" s="6"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="12"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
@@ -6819,8 +6878,8 @@
       <c r="X110" s="1"/>
     </row>
     <row r="111" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="7"/>
-      <c r="C111" s="8"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="14"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1" t="s">
@@ -6872,10 +6931,10 @@
     </row>
     <row r="113" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="114" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C114" s="4"/>
+      <c r="C114" s="10"/>
       <c r="E114" s="1" t="s">
         <v>32</v>
       </c>
@@ -6926,8 +6985,8 @@
       <c r="X114" s="1"/>
     </row>
     <row r="115" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B115" s="5"/>
-      <c r="C115" s="6"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="12"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1" t="s">
@@ -6968,8 +7027,8 @@
       <c r="X115" s="1"/>
     </row>
     <row r="116" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B116" s="5"/>
-      <c r="C116" s="6"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="12"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
@@ -7004,8 +7063,8 @@
       <c r="X116" s="1"/>
     </row>
     <row r="117" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="7"/>
-      <c r="C117" s="8"/>
+      <c r="B117" s="13"/>
+      <c r="C117" s="14"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1" t="s">
@@ -7055,10 +7114,10 @@
     </row>
     <row r="119" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B120" s="9" t="s">
+      <c r="B120" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C120" s="10"/>
+      <c r="C120" s="4"/>
       <c r="E120" s="1" t="s">
         <v>32</v>
       </c>
@@ -7097,8 +7156,8 @@
       <c r="X120" s="1"/>
     </row>
     <row r="121" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B121" s="11"/>
-      <c r="C121" s="12"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="6"/>
       <c r="E121" s="1" t="s">
         <v>11</v>
       </c>
@@ -7147,8 +7206,8 @@
       <c r="X121" s="1"/>
     </row>
     <row r="122" spans="2:24" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B122" s="11"/>
-      <c r="C122" s="12"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="6"/>
       <c r="E122" s="1" t="s">
         <v>2</v>
       </c>
@@ -7185,8 +7244,8 @@
       <c r="X122" s="1"/>
     </row>
     <row r="123" spans="2:24" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="13"/>
-      <c r="C123" s="14"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="8"/>
       <c r="E123" s="1" t="s">
         <v>6</v>
       </c>
@@ -7244,11 +7303,15 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="Z32:AA35"/>
-    <mergeCell ref="Z37:AA40"/>
-    <mergeCell ref="Z43:AA46"/>
-    <mergeCell ref="Z57:AA60"/>
-    <mergeCell ref="Z62:AA65"/>
+    <mergeCell ref="B108:C111"/>
+    <mergeCell ref="B102:C105"/>
+    <mergeCell ref="Z79:AA82"/>
+    <mergeCell ref="Z74:AA77"/>
+    <mergeCell ref="B114:C117"/>
+    <mergeCell ref="Z86:AA89"/>
+    <mergeCell ref="B86:C89"/>
+    <mergeCell ref="B80:C83"/>
+    <mergeCell ref="B73:C76"/>
     <mergeCell ref="Z69:AA72"/>
     <mergeCell ref="B120:C123"/>
     <mergeCell ref="B4:C7"/>
@@ -7265,15 +7328,11 @@
     <mergeCell ref="Z27:AA30"/>
     <mergeCell ref="B68:C71"/>
     <mergeCell ref="B96:C99"/>
-    <mergeCell ref="B108:C111"/>
-    <mergeCell ref="B102:C105"/>
-    <mergeCell ref="Z79:AA82"/>
-    <mergeCell ref="Z74:AA77"/>
-    <mergeCell ref="B114:C117"/>
-    <mergeCell ref="Z86:AA89"/>
-    <mergeCell ref="B86:C89"/>
-    <mergeCell ref="B80:C83"/>
-    <mergeCell ref="B73:C76"/>
+    <mergeCell ref="Z32:AA35"/>
+    <mergeCell ref="Z37:AA40"/>
+    <mergeCell ref="Z43:AA46"/>
+    <mergeCell ref="Z57:AA60"/>
+    <mergeCell ref="Z62:AA65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -7285,6 +7344,8 @@
   <dimension ref="B16:EA130"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="29" max="29" width="15.42578125" customWidth="1"/>
     <col min="56" max="56" width="27" customWidth="1"/>
     <col min="83" max="83" width="33.7109375" customWidth="1"/>
@@ -7294,10 +7355,10 @@
   <sheetData>
     <row r="16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE17" s="9" t="s">
+      <c r="DE17" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="DF17" s="10"/>
+      <c r="DF17" s="4"/>
       <c r="DH17" s="1" t="s">
         <v>32</v>
       </c>
@@ -7348,8 +7409,8 @@
       <c r="EA17" s="1"/>
     </row>
     <row r="18" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE18" s="11"/>
-      <c r="DF18" s="12"/>
+      <c r="DE18" s="5"/>
+      <c r="DF18" s="6"/>
       <c r="DH18" s="1"/>
       <c r="DI18" s="1"/>
       <c r="DJ18" s="1" t="s">
@@ -7394,10 +7455,10 @@
       <c r="EA18" s="1"/>
     </row>
     <row r="19" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD19" s="9" t="s">
+      <c r="CD19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="CE19" s="10"/>
+      <c r="CE19" s="4"/>
       <c r="CG19" s="1" t="s">
         <v>32</v>
       </c>
@@ -7434,8 +7495,8 @@
       <c r="CX19" s="1"/>
       <c r="CY19" s="1"/>
       <c r="CZ19" s="1"/>
-      <c r="DE19" s="11"/>
-      <c r="DF19" s="12"/>
+      <c r="DE19" s="5"/>
+      <c r="DF19" s="6"/>
       <c r="DH19" s="1"/>
       <c r="DI19" s="1"/>
       <c r="DJ19" s="1"/>
@@ -7458,8 +7519,8 @@
       <c r="EA19" s="1"/>
     </row>
     <row r="20" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD20" s="11"/>
-      <c r="CE20" s="12"/>
+      <c r="CD20" s="5"/>
+      <c r="CE20" s="6"/>
       <c r="CG20" s="1" t="s">
         <v>11</v>
       </c>
@@ -7506,8 +7567,8 @@
       <c r="CX20" s="1"/>
       <c r="CY20" s="1"/>
       <c r="CZ20" s="1"/>
-      <c r="DE20" s="13"/>
-      <c r="DF20" s="14"/>
+      <c r="DE20" s="7"/>
+      <c r="DF20" s="8"/>
       <c r="DH20" s="1"/>
       <c r="DI20" s="1"/>
       <c r="DJ20" s="1"/>
@@ -7530,8 +7591,8 @@
       <c r="EA20" s="1"/>
     </row>
     <row r="21" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD21" s="11"/>
-      <c r="CE21" s="12"/>
+      <c r="CD21" s="5"/>
+      <c r="CE21" s="6"/>
       <c r="CG21" s="1" t="s">
         <v>2</v>
       </c>
@@ -7568,8 +7629,8 @@
       <c r="CZ21" s="1"/>
     </row>
     <row r="22" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD22" s="13"/>
-      <c r="CE22" s="14"/>
+      <c r="CD22" s="7"/>
+      <c r="CE22" s="8"/>
       <c r="CG22" s="1" t="s">
         <v>6</v>
       </c>
@@ -7626,10 +7687,10 @@
       <c r="CZ22" s="1"/>
     </row>
     <row r="23" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE23" s="3" t="s">
+      <c r="DE23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="DF23" s="4"/>
+      <c r="DF23" s="10"/>
       <c r="DH23" s="1" t="s">
         <v>32</v>
       </c>
@@ -7680,8 +7741,8 @@
       <c r="EA23" s="1"/>
     </row>
     <row r="24" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE24" s="5"/>
-      <c r="DF24" s="6"/>
+      <c r="DE24" s="11"/>
+      <c r="DF24" s="12"/>
       <c r="DH24" s="1"/>
       <c r="DI24" s="1"/>
       <c r="DJ24" s="1" t="s">
@@ -7730,8 +7791,8 @@
       <c r="EA24" s="1"/>
     </row>
     <row r="25" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="6"/>
+      <c r="DE25" s="11"/>
+      <c r="DF25" s="12"/>
       <c r="DH25" s="1"/>
       <c r="DI25" s="1"/>
       <c r="DJ25" s="1" t="s">
@@ -7776,8 +7837,8 @@
       <c r="EA25" s="1"/>
     </row>
     <row r="26" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE26" s="7"/>
-      <c r="DF26" s="8"/>
+      <c r="DE26" s="13"/>
+      <c r="DF26" s="14"/>
       <c r="DH26" s="1"/>
       <c r="DI26" s="1"/>
       <c r="DJ26" s="1"/>
@@ -7801,10 +7862,10 @@
     </row>
     <row r="27" spans="82:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD28" s="9" t="s">
+      <c r="CD28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="CE28" s="10"/>
+      <c r="CE28" s="4"/>
       <c r="CG28" s="1" t="s">
         <v>32</v>
       </c>
@@ -7845,8 +7906,8 @@
       <c r="CZ28" s="1"/>
     </row>
     <row r="29" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD29" s="11"/>
-      <c r="CE29" s="12"/>
+      <c r="CD29" s="5"/>
+      <c r="CE29" s="6"/>
       <c r="CG29" s="1" t="s">
         <v>11</v>
       </c>
@@ -7887,10 +7948,10 @@
       <c r="CX29" s="1"/>
       <c r="CY29" s="1"/>
       <c r="CZ29" s="1"/>
-      <c r="DE29" s="3" t="s">
+      <c r="DE29" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="DF29" s="4"/>
+      <c r="DF29" s="10"/>
       <c r="DH29" s="1" t="s">
         <v>32</v>
       </c>
@@ -7941,8 +8002,8 @@
       <c r="EA29" s="1"/>
     </row>
     <row r="30" spans="82:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD30" s="11"/>
-      <c r="CE30" s="12"/>
+      <c r="CD30" s="5"/>
+      <c r="CE30" s="6"/>
       <c r="CG30" s="1" t="s">
         <v>2</v>
       </c>
@@ -7995,8 +8056,8 @@
       <c r="CZ30" s="1">
         <v>0</v>
       </c>
-      <c r="DE30" s="5"/>
-      <c r="DF30" s="6"/>
+      <c r="DE30" s="11"/>
+      <c r="DF30" s="12"/>
       <c r="DH30" s="1"/>
       <c r="DI30" s="1"/>
       <c r="DJ30" s="1" t="s">
@@ -8037,8 +8098,8 @@
       <c r="EA30" s="1"/>
     </row>
     <row r="31" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD31" s="13"/>
-      <c r="CE31" s="14"/>
+      <c r="CD31" s="7"/>
+      <c r="CE31" s="8"/>
       <c r="CG31" s="1" t="s">
         <v>2</v>
       </c>
@@ -8089,8 +8150,8 @@
       <c r="CZ31" s="1">
         <v>2</v>
       </c>
-      <c r="DE31" s="5"/>
-      <c r="DF31" s="6"/>
+      <c r="DE31" s="11"/>
+      <c r="DF31" s="12"/>
       <c r="DH31" s="1"/>
       <c r="DI31" s="1"/>
       <c r="DJ31" s="1" t="s">
@@ -8125,8 +8186,8 @@
       <c r="EA31" s="1"/>
     </row>
     <row r="32" spans="82:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE32" s="7"/>
-      <c r="DF32" s="8"/>
+      <c r="DE32" s="13"/>
+      <c r="DF32" s="14"/>
       <c r="DH32" s="1"/>
       <c r="DI32" s="1"/>
       <c r="DJ32" s="1" t="s">
@@ -8178,10 +8239,10 @@
     </row>
     <row r="33" spans="55:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC34" s="9" t="s">
+      <c r="BC34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BD34" s="10"/>
+      <c r="BD34" s="4"/>
       <c r="BF34" s="1" t="s">
         <v>32</v>
       </c>
@@ -8218,10 +8279,10 @@
       <c r="BW34" s="1"/>
       <c r="BX34" s="1"/>
       <c r="BY34" s="1"/>
-      <c r="CD34" s="9" t="s">
+      <c r="CD34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="CE34" s="10"/>
+      <c r="CE34" s="4"/>
       <c r="CG34" s="1" t="s">
         <v>2</v>
       </c>
@@ -8266,8 +8327,8 @@
       <c r="CZ34" s="1"/>
     </row>
     <row r="35" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC35" s="11"/>
-      <c r="BD35" s="12"/>
+      <c r="BC35" s="5"/>
+      <c r="BD35" s="6"/>
       <c r="BF35" s="1"/>
       <c r="BG35" s="1"/>
       <c r="BH35" s="1" t="s">
@@ -8318,8 +8379,8 @@
       </c>
       <c r="BX35" s="1"/>
       <c r="BY35" s="1"/>
-      <c r="CD35" s="11"/>
-      <c r="CE35" s="12"/>
+      <c r="CD35" s="5"/>
+      <c r="CE35" s="6"/>
       <c r="CG35" s="1" t="s">
         <v>2</v>
       </c>
@@ -8366,10 +8427,10 @@
       <c r="CZ35" s="1">
         <v>1</v>
       </c>
-      <c r="DE35" s="3" t="s">
+      <c r="DE35" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="DF35" s="4"/>
+      <c r="DF35" s="10"/>
       <c r="DH35" s="1" t="s">
         <v>32</v>
       </c>
@@ -8420,8 +8481,8 @@
       <c r="EA35" s="1"/>
     </row>
     <row r="36" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC36" s="11"/>
-      <c r="BD36" s="12"/>
+      <c r="BC36" s="5"/>
+      <c r="BD36" s="6"/>
       <c r="BF36" s="1"/>
       <c r="BG36" s="1"/>
       <c r="BH36" s="1" t="s">
@@ -8458,8 +8519,8 @@
       <c r="BW36" s="1"/>
       <c r="BX36" s="1"/>
       <c r="BY36" s="1"/>
-      <c r="CD36" s="11"/>
-      <c r="CE36" s="12"/>
+      <c r="CD36" s="5"/>
+      <c r="CE36" s="6"/>
       <c r="CG36" s="1" t="s">
         <v>8</v>
       </c>
@@ -8502,8 +8563,8 @@
       <c r="CX36" s="1"/>
       <c r="CY36" s="1"/>
       <c r="CZ36" s="1"/>
-      <c r="DE36" s="5"/>
-      <c r="DF36" s="6"/>
+      <c r="DE36" s="11"/>
+      <c r="DF36" s="12"/>
       <c r="DH36" s="1"/>
       <c r="DI36" s="1"/>
       <c r="DJ36" s="1" t="s">
@@ -8544,8 +8605,8 @@
       <c r="EA36" s="1"/>
     </row>
     <row r="37" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC37" s="13"/>
-      <c r="BD37" s="14"/>
+      <c r="BC37" s="7"/>
+      <c r="BD37" s="8"/>
       <c r="BF37" s="1"/>
       <c r="BG37" s="1"/>
       <c r="BH37" s="1" t="s">
@@ -8582,8 +8643,8 @@
       <c r="BW37" s="1"/>
       <c r="BX37" s="1"/>
       <c r="BY37" s="1"/>
-      <c r="CD37" s="13"/>
-      <c r="CE37" s="14"/>
+      <c r="CD37" s="7"/>
+      <c r="CE37" s="8"/>
       <c r="CG37" s="1" t="s">
         <v>8</v>
       </c>
@@ -8626,8 +8687,8 @@
       <c r="CX37" s="1"/>
       <c r="CY37" s="1"/>
       <c r="CZ37" s="1"/>
-      <c r="DE37" s="5"/>
-      <c r="DF37" s="6"/>
+      <c r="DE37" s="11"/>
+      <c r="DF37" s="12"/>
       <c r="DH37" s="1"/>
       <c r="DI37" s="1"/>
       <c r="DJ37" s="1" t="s">
@@ -8662,8 +8723,8 @@
       <c r="EA37" s="1"/>
     </row>
     <row r="38" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE38" s="7"/>
-      <c r="DF38" s="8"/>
+      <c r="DE38" s="13"/>
+      <c r="DF38" s="14"/>
       <c r="DH38" s="1"/>
       <c r="DI38" s="1"/>
       <c r="DJ38" s="1" t="s">
@@ -8712,10 +8773,10 @@
       <c r="EA38" s="1"/>
     </row>
     <row r="39" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC39" s="9" t="s">
+      <c r="BC39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BD39" s="10"/>
+      <c r="BD39" s="4"/>
       <c r="BF39" s="1" t="s">
         <v>32</v>
       </c>
@@ -8756,8 +8817,8 @@
       <c r="BY39" s="1"/>
     </row>
     <row r="40" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC40" s="11"/>
-      <c r="BD40" s="12"/>
+      <c r="BC40" s="5"/>
+      <c r="BD40" s="6"/>
       <c r="BF40" s="1"/>
       <c r="BG40" s="1"/>
       <c r="BH40" s="1" t="s">
@@ -8796,8 +8857,8 @@
       <c r="BY40" s="1"/>
     </row>
     <row r="41" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC41" s="11"/>
-      <c r="BD41" s="12"/>
+      <c r="BC41" s="5"/>
+      <c r="BD41" s="6"/>
       <c r="BF41" s="1"/>
       <c r="BG41" s="1"/>
       <c r="BH41" s="1" t="s">
@@ -8836,8 +8897,8 @@
       <c r="BY41" s="1"/>
     </row>
     <row r="42" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC42" s="13"/>
-      <c r="BD42" s="14"/>
+      <c r="BC42" s="7"/>
+      <c r="BD42" s="8"/>
       <c r="BF42" s="1"/>
       <c r="BG42" s="1"/>
       <c r="BH42" s="1" t="s">
@@ -8874,10 +8935,10 @@
       <c r="BW42" s="1"/>
       <c r="BX42" s="1"/>
       <c r="BY42" s="1"/>
-      <c r="CD42" s="9" t="s">
+      <c r="CD42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="CE42" s="10"/>
+      <c r="CE42" s="4"/>
       <c r="CG42" s="1" t="s">
         <v>32</v>
       </c>
@@ -8916,8 +8977,8 @@
       <c r="CZ42" s="1"/>
     </row>
     <row r="43" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD43" s="11"/>
-      <c r="CE43" s="12"/>
+      <c r="CD43" s="5"/>
+      <c r="CE43" s="6"/>
       <c r="CG43" s="1"/>
       <c r="CH43" s="1"/>
       <c r="CI43" s="1" t="s">
@@ -8952,8 +9013,8 @@
       <c r="CZ43" s="1"/>
     </row>
     <row r="44" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD44" s="11"/>
-      <c r="CE44" s="12"/>
+      <c r="CD44" s="5"/>
+      <c r="CE44" s="6"/>
       <c r="CG44" s="1"/>
       <c r="CH44" s="1"/>
       <c r="CI44" s="1" t="s">
@@ -8988,8 +9049,8 @@
       <c r="CZ44" s="1"/>
     </row>
     <row r="45" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD45" s="13"/>
-      <c r="CE45" s="14"/>
+      <c r="CD45" s="7"/>
+      <c r="CE45" s="8"/>
       <c r="CG45" s="1"/>
       <c r="CH45" s="1"/>
       <c r="CI45" s="1" t="s">
@@ -9024,10 +9085,10 @@
       <c r="CZ45" s="1"/>
     </row>
     <row r="46" spans="55:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE46" s="9" t="s">
+      <c r="DE46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="DF46" s="10"/>
+      <c r="DF46" s="4"/>
       <c r="DH46" s="1" t="s">
         <v>32</v>
       </c>
@@ -9066,10 +9127,10 @@
       <c r="EA46" s="1"/>
     </row>
     <row r="47" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD47" s="9" t="s">
+      <c r="CD47" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="CE47" s="10"/>
+      <c r="CE47" s="4"/>
       <c r="CG47" s="1" t="s">
         <v>32</v>
       </c>
@@ -9104,8 +9165,8 @@
       <c r="CX47" s="1"/>
       <c r="CY47" s="1"/>
       <c r="CZ47" s="1"/>
-      <c r="DE47" s="11"/>
-      <c r="DF47" s="12"/>
+      <c r="DE47" s="5"/>
+      <c r="DF47" s="6"/>
       <c r="DH47" s="1"/>
       <c r="DI47" s="1"/>
       <c r="DJ47" s="1" t="s">
@@ -9146,8 +9207,8 @@
       <c r="EA47" s="1"/>
     </row>
     <row r="48" spans="55:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD48" s="11"/>
-      <c r="CE48" s="12"/>
+      <c r="CD48" s="5"/>
+      <c r="CE48" s="6"/>
       <c r="CG48" s="1"/>
       <c r="CH48" s="1"/>
       <c r="CI48" s="1"/>
@@ -9168,8 +9229,8 @@
       <c r="CX48" s="1"/>
       <c r="CY48" s="1"/>
       <c r="CZ48" s="1"/>
-      <c r="DE48" s="11"/>
-      <c r="DF48" s="12"/>
+      <c r="DE48" s="5"/>
+      <c r="DF48" s="6"/>
       <c r="DH48" s="1"/>
       <c r="DI48" s="1"/>
       <c r="DJ48" s="1" t="s">
@@ -9209,9 +9270,9 @@
       <c r="DZ48" s="1"/>
       <c r="EA48" s="1"/>
     </row>
-    <row r="49" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD49" s="11"/>
-      <c r="CE49" s="12"/>
+    <row r="49" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD49" s="5"/>
+      <c r="CE49" s="6"/>
       <c r="CG49" s="1"/>
       <c r="CH49" s="1"/>
       <c r="CI49" s="1"/>
@@ -9232,8 +9293,8 @@
       <c r="CX49" s="1"/>
       <c r="CY49" s="1"/>
       <c r="CZ49" s="1"/>
-      <c r="DE49" s="13"/>
-      <c r="DF49" s="14"/>
+      <c r="DE49" s="7"/>
+      <c r="DF49" s="8"/>
       <c r="DH49" s="1"/>
       <c r="DI49" s="1"/>
       <c r="DJ49" s="1" t="s">
@@ -9275,9 +9336,9 @@
       <c r="DZ49" s="1"/>
       <c r="EA49" s="1"/>
     </row>
-    <row r="50" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD50" s="13"/>
-      <c r="CE50" s="14"/>
+    <row r="50" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD50" s="7"/>
+      <c r="CE50" s="8"/>
       <c r="CG50" s="1"/>
       <c r="CH50" s="1"/>
       <c r="CI50" s="1"/>
@@ -9299,11 +9360,11 @@
       <c r="CY50" s="1"/>
       <c r="CZ50" s="1"/>
     </row>
-    <row r="51" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="DE51" s="9" t="s">
+    <row r="51" spans="2:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="DE51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="DF51" s="10"/>
+      <c r="DF51" s="4"/>
       <c r="DH51" s="1" t="s">
         <v>32</v>
       </c>
@@ -9341,9 +9402,9 @@
       <c r="DZ51" s="1"/>
       <c r="EA51" s="1"/>
     </row>
-    <row r="52" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="DE52" s="11"/>
-      <c r="DF52" s="12"/>
+    <row r="52" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="DE52" s="5"/>
+      <c r="DF52" s="6"/>
       <c r="DH52" s="1"/>
       <c r="DI52" s="1"/>
       <c r="DJ52" s="1" t="s">
@@ -9391,11 +9452,11 @@
       <c r="DZ52" s="1"/>
       <c r="EA52" s="1"/>
     </row>
-    <row r="53" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD53" s="9" t="s">
+    <row r="53" spans="2:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="CD53" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="CE53" s="10"/>
+      <c r="CE53" s="4"/>
       <c r="CG53" s="1" t="s">
         <v>32</v>
       </c>
@@ -9432,8 +9493,8 @@
       <c r="CX53" s="1"/>
       <c r="CY53" s="1"/>
       <c r="CZ53" s="1"/>
-      <c r="DE53" s="11"/>
-      <c r="DF53" s="12"/>
+      <c r="DE53" s="5"/>
+      <c r="DF53" s="6"/>
       <c r="DH53" s="1"/>
       <c r="DI53" s="1"/>
       <c r="DJ53" s="1" t="s">
@@ -9479,9 +9540,9 @@
       <c r="DZ53" s="1"/>
       <c r="EA53" s="1"/>
     </row>
-    <row r="54" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD54" s="11"/>
-      <c r="CE54" s="12"/>
+    <row r="54" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD54" s="5"/>
+      <c r="CE54" s="6"/>
       <c r="CG54" s="1"/>
       <c r="CH54" s="1"/>
       <c r="CI54" s="1" t="s">
@@ -9530,8 +9591,8 @@
       </c>
       <c r="CY54" s="1"/>
       <c r="CZ54" s="1"/>
-      <c r="DE54" s="13"/>
-      <c r="DF54" s="14"/>
+      <c r="DE54" s="7"/>
+      <c r="DF54" s="8"/>
       <c r="DH54" s="1"/>
       <c r="DI54" s="1"/>
       <c r="DJ54" s="1"/>
@@ -9553,11 +9614,11 @@
       <c r="DZ54" s="1"/>
       <c r="EA54" s="1"/>
     </row>
-    <row r="55" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC55" s="9" t="s">
+    <row r="55" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BC55" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="BD55" s="10"/>
+      <c r="BD55" s="4"/>
       <c r="BF55" s="1" t="s">
         <v>32</v>
       </c>
@@ -9594,8 +9655,8 @@
       <c r="BW55" s="1"/>
       <c r="BX55" s="1"/>
       <c r="BY55" s="1"/>
-      <c r="CD55" s="11"/>
-      <c r="CE55" s="12"/>
+      <c r="CD55" s="5"/>
+      <c r="CE55" s="6"/>
       <c r="CG55" s="1"/>
       <c r="CH55" s="1"/>
       <c r="CI55" s="1" t="s">
@@ -9645,9 +9706,51 @@
       <c r="CY55" s="1"/>
       <c r="CZ55" s="1"/>
     </row>
-    <row r="56" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC56" s="11"/>
-      <c r="BD56" s="12"/>
+    <row r="56" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="E56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="BC56" s="5"/>
+      <c r="BD56" s="6"/>
       <c r="BF56" s="1"/>
       <c r="BG56" s="1"/>
       <c r="BH56" s="1" t="s">
@@ -9684,8 +9787,8 @@
       <c r="BW56" s="1"/>
       <c r="BX56" s="1"/>
       <c r="BY56" s="1"/>
-      <c r="CD56" s="13"/>
-      <c r="CE56" s="14"/>
+      <c r="CD56" s="7"/>
+      <c r="CE56" s="8"/>
       <c r="CG56" s="1"/>
       <c r="CH56" s="1"/>
       <c r="CI56" s="1" t="s">
@@ -9735,9 +9838,51 @@
       <c r="CY56" s="1"/>
       <c r="CZ56" s="1"/>
     </row>
-    <row r="57" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC57" s="11"/>
-      <c r="BD57" s="12"/>
+    <row r="57" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="5"/>
+      <c r="C57" s="6"/>
+      <c r="E57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="BC57" s="5"/>
+      <c r="BD57" s="6"/>
       <c r="BF57" s="1"/>
       <c r="BG57" s="1"/>
       <c r="BH57" s="1" t="s">
@@ -9781,9 +9926,45 @@
       <c r="BX57" s="1"/>
       <c r="BY57" s="1"/>
     </row>
-    <row r="58" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC58" s="13"/>
-      <c r="BD58" s="14"/>
+    <row r="58" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="BC58" s="7"/>
+      <c r="BD58" s="8"/>
       <c r="BF58" s="1"/>
       <c r="BG58" s="1"/>
       <c r="BH58" s="1" t="s">
@@ -9820,10 +10001,10 @@
       <c r="BW58" s="1"/>
       <c r="BX58" s="1"/>
       <c r="BY58" s="1"/>
-      <c r="CD58" s="9" t="s">
+      <c r="CD58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="CE58" s="10"/>
+      <c r="CE58" s="4"/>
       <c r="CG58" s="1" t="s">
         <v>32</v>
       </c>
@@ -9875,9 +10056,51 @@
       <c r="CY58" s="1"/>
       <c r="CZ58" s="1"/>
     </row>
-    <row r="59" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD59" s="11"/>
-      <c r="CE59" s="12"/>
+    <row r="59" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U59" s="1">
+        <v>1</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W59" s="1">
+        <v>0</v>
+      </c>
+      <c r="X59" s="1"/>
+      <c r="CD59" s="5"/>
+      <c r="CE59" s="6"/>
       <c r="CG59" s="1"/>
       <c r="CH59" s="1"/>
       <c r="CI59" s="1"/>
@@ -9899,9 +10122,9 @@
       <c r="CY59" s="1"/>
       <c r="CZ59" s="1"/>
     </row>
-    <row r="60" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="CD60" s="11"/>
-      <c r="CE60" s="12"/>
+    <row r="60" spans="2:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="CD60" s="5"/>
+      <c r="CE60" s="6"/>
       <c r="CG60" s="1"/>
       <c r="CH60" s="1"/>
       <c r="CI60" s="1"/>
@@ -9923,9 +10146,9 @@
       <c r="CY60" s="1"/>
       <c r="CZ60" s="1"/>
     </row>
-    <row r="61" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD61" s="13"/>
-      <c r="CE61" s="14"/>
+    <row r="61" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD61" s="7"/>
+      <c r="CE61" s="8"/>
       <c r="CG61" s="1"/>
       <c r="CH61" s="1"/>
       <c r="CI61" s="1"/>
@@ -9947,12 +10170,12 @@
       <c r="CY61" s="1"/>
       <c r="CZ61" s="1"/>
     </row>
-    <row r="62" spans="28:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="28:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD63" s="9" t="s">
+    <row r="62" spans="2:131" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="2:131" ht="33" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CD63" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="CE63" s="10"/>
+      <c r="CE63" s="4"/>
       <c r="CG63" s="1" t="s">
         <v>32</v>
       </c>
@@ -9990,11 +10213,65 @@
       <c r="CY63" s="1"/>
       <c r="CZ63" s="1"/>
     </row>
-    <row r="64" spans="28:131" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="AB64" s="9" t="s">
+    <row r="64" spans="2:131" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="B64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X64" s="1"/>
+      <c r="AB64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AC64" s="10"/>
+      <c r="AC64" s="4"/>
       <c r="AE64" s="1" t="s">
         <v>32</v>
       </c>
@@ -10035,8 +10312,8 @@
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
       <c r="AX64" s="1"/>
-      <c r="CD64" s="11"/>
-      <c r="CE64" s="12"/>
+      <c r="CD64" s="5"/>
+      <c r="CE64" s="6"/>
       <c r="CG64" s="1"/>
       <c r="CH64" s="1"/>
       <c r="CI64" s="1" t="s">
@@ -10085,8 +10362,62 @@
       <c r="CZ64" s="1"/>
     </row>
     <row r="65" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="AB65" s="11"/>
-      <c r="AC65" s="12"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="6"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X65" s="1"/>
+      <c r="AB65" s="5"/>
+      <c r="AC65" s="6"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
       <c r="AG65" s="1" t="s">
@@ -10119,8 +10450,8 @@
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
       <c r="AX65" s="1"/>
-      <c r="CD65" s="11"/>
-      <c r="CE65" s="12"/>
+      <c r="CD65" s="5"/>
+      <c r="CE65" s="6"/>
       <c r="CG65" s="1"/>
       <c r="CH65" s="1"/>
       <c r="CI65" s="1" t="s">
@@ -10169,8 +10500,64 @@
       <c r="CZ65" s="1"/>
     </row>
     <row r="66" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB66" s="11"/>
-      <c r="AC66" s="12"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6"/>
+      <c r="E66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB66" s="5"/>
+      <c r="AC66" s="6"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
       <c r="AG66" s="1" t="s">
@@ -10205,8 +10592,8 @@
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
       <c r="AX66" s="1"/>
-      <c r="CD66" s="13"/>
-      <c r="CE66" s="14"/>
+      <c r="CD66" s="7"/>
+      <c r="CE66" s="8"/>
       <c r="CG66" s="1"/>
       <c r="CH66" s="1"/>
       <c r="CI66" s="1" t="s">
@@ -10255,50 +10642,62 @@
       <c r="CZ66" s="1"/>
     </row>
     <row r="67" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="E67" s="1" t="s">
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W67" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="X67" s="1"/>
-      <c r="AB67" s="13"/>
-      <c r="AC67" s="14"/>
+      <c r="AB67" s="7"/>
+      <c r="AC67" s="8"/>
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
       <c r="AG67" s="1" t="s">
@@ -10335,52 +10734,10 @@
       <c r="AX67" s="1"/>
     </row>
     <row r="68" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="E68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
-      <c r="BC68" s="9" t="s">
+      <c r="BC68" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BD68" s="10"/>
+      <c r="BD68" s="4"/>
       <c r="BF68" s="1" t="s">
         <v>32</v>
       </c>
@@ -10417,10 +10774,10 @@
       <c r="BW68" s="1"/>
       <c r="BX68" s="1"/>
       <c r="BY68" s="1"/>
-      <c r="CD68" s="9" t="s">
+      <c r="CD68" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="CE68" s="10"/>
+      <c r="CE68" s="4"/>
       <c r="CG68" s="1" t="s">
         <v>32</v>
       </c>
@@ -10471,29 +10828,17 @@
       <c r="CZ68" s="1"/>
     </row>
     <row r="69" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="E69" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="B69" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
@@ -10507,10 +10852,10 @@
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
-      <c r="AB69" s="9" t="s">
+      <c r="AB69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AC69" s="10"/>
+      <c r="AC69" s="4"/>
       <c r="AE69" s="1" t="s">
         <v>32</v>
       </c>
@@ -10557,8 +10902,8 @@
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
       <c r="AX69" s="1"/>
-      <c r="BC69" s="11"/>
-      <c r="BD69" s="12"/>
+      <c r="BC69" s="5"/>
+      <c r="BD69" s="6"/>
       <c r="BF69" s="1"/>
       <c r="BG69" s="1"/>
       <c r="BH69" s="1" t="s">
@@ -10593,8 +10938,8 @@
       <c r="BW69" s="1"/>
       <c r="BX69" s="1"/>
       <c r="BY69" s="1"/>
-      <c r="CD69" s="11"/>
-      <c r="CE69" s="12"/>
+      <c r="CD69" s="5"/>
+      <c r="CE69" s="6"/>
       <c r="CG69" s="1"/>
       <c r="CH69" s="1"/>
       <c r="CI69" s="1"/>
@@ -10616,51 +10961,59 @@
       <c r="CY69" s="1"/>
       <c r="CZ69" s="1"/>
     </row>
-    <row r="70" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="13"/>
-      <c r="C70" s="14"/>
-      <c r="E70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>26</v>
-      </c>
+    <row r="70" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
       <c r="H70" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="T70" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U70" s="1">
-        <v>1</v>
-      </c>
-      <c r="V70" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W70" s="1">
-        <v>0</v>
-      </c>
+      <c r="U70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
       <c r="X70" s="1"/>
-      <c r="AB70" s="11"/>
-      <c r="AC70" s="12"/>
+      <c r="AB70" s="5"/>
+      <c r="AC70" s="6"/>
       <c r="AE70" s="1"/>
       <c r="AF70" s="1"/>
       <c r="AG70" s="1" t="s">
@@ -10697,8 +11050,8 @@
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
       <c r="AX70" s="1"/>
-      <c r="BC70" s="11"/>
-      <c r="BD70" s="12"/>
+      <c r="BC70" s="5"/>
+      <c r="BD70" s="6"/>
       <c r="BF70" s="1"/>
       <c r="BG70" s="1"/>
       <c r="BH70" s="1" t="s">
@@ -10733,8 +11086,8 @@
       <c r="BW70" s="1"/>
       <c r="BX70" s="1"/>
       <c r="BY70" s="1"/>
-      <c r="CD70" s="11"/>
-      <c r="CE70" s="12"/>
+      <c r="CD70" s="5"/>
+      <c r="CE70" s="6"/>
       <c r="CG70" s="1"/>
       <c r="CH70" s="1"/>
       <c r="CI70" s="1"/>
@@ -10757,8 +11110,30 @@
       <c r="CZ70" s="1"/>
     </row>
     <row r="71" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB71" s="11"/>
-      <c r="AC71" s="12"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="AB71" s="5"/>
+      <c r="AC71" s="6"/>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1"/>
       <c r="AG71" s="1" t="s">
@@ -10795,8 +11170,8 @@
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
       <c r="AX71" s="1"/>
-      <c r="BC71" s="13"/>
-      <c r="BD71" s="14"/>
+      <c r="BC71" s="7"/>
+      <c r="BD71" s="8"/>
       <c r="BF71" s="1"/>
       <c r="BG71" s="1"/>
       <c r="BH71" s="1"/>
@@ -10817,8 +11192,8 @@
       <c r="BW71" s="1"/>
       <c r="BX71" s="1"/>
       <c r="BY71" s="1"/>
-      <c r="CD71" s="13"/>
-      <c r="CE71" s="14"/>
+      <c r="CD71" s="7"/>
+      <c r="CE71" s="8"/>
       <c r="CG71" s="1"/>
       <c r="CH71" s="1"/>
       <c r="CI71" s="1"/>
@@ -10841,8 +11216,30 @@
       <c r="CZ71" s="1"/>
     </row>
     <row r="72" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB72" s="13"/>
-      <c r="AC72" s="14"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="8"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="AB72" s="7"/>
+      <c r="AC72" s="8"/>
       <c r="AE72" s="1"/>
       <c r="AF72" s="1"/>
       <c r="AG72" s="1" t="s">
@@ -10874,10 +11271,10 @@
     </row>
     <row r="73" spans="2:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="74" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC74" s="9" t="s">
+      <c r="BC74" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BD74" s="10"/>
+      <c r="BD74" s="4"/>
       <c r="BF74" s="1" t="s">
         <v>32</v>
       </c>
@@ -10916,8 +11313,8 @@
       <c r="BY74" s="1"/>
     </row>
     <row r="75" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC75" s="11"/>
-      <c r="BD75" s="12"/>
+      <c r="BC75" s="5"/>
+      <c r="BD75" s="6"/>
       <c r="BF75" s="1"/>
       <c r="BG75" s="1"/>
       <c r="BH75" s="1" t="s">
@@ -10956,10 +11353,10 @@
       </c>
       <c r="BX75" s="1"/>
       <c r="BY75" s="1"/>
-      <c r="CD75" s="9" t="s">
+      <c r="CD75" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="CE75" s="10"/>
+      <c r="CE75" s="4"/>
       <c r="CG75" s="1" t="s">
         <v>32</v>
       </c>
@@ -10998,8 +11395,8 @@
       <c r="CZ75" s="1"/>
     </row>
     <row r="76" spans="2:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC76" s="11"/>
-      <c r="BD76" s="12"/>
+      <c r="BC76" s="5"/>
+      <c r="BD76" s="6"/>
       <c r="BF76" s="1"/>
       <c r="BG76" s="1"/>
       <c r="BH76" s="1" t="s">
@@ -11038,8 +11435,8 @@
       </c>
       <c r="BX76" s="1"/>
       <c r="BY76" s="1"/>
-      <c r="CD76" s="11"/>
-      <c r="CE76" s="12"/>
+      <c r="CD76" s="5"/>
+      <c r="CE76" s="6"/>
       <c r="CG76" s="1"/>
       <c r="CH76" s="1"/>
       <c r="CI76" s="1" t="s">
@@ -11080,8 +11477,8 @@
       <c r="CZ76" s="1"/>
     </row>
     <row r="77" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC77" s="13"/>
-      <c r="BD77" s="14"/>
+      <c r="BC77" s="7"/>
+      <c r="BD77" s="8"/>
       <c r="BF77" s="1"/>
       <c r="BG77" s="1"/>
       <c r="BH77" s="1"/>
@@ -11102,8 +11499,8 @@
       <c r="BW77" s="1"/>
       <c r="BX77" s="1"/>
       <c r="BY77" s="1"/>
-      <c r="CD77" s="11"/>
-      <c r="CE77" s="12"/>
+      <c r="CD77" s="5"/>
+      <c r="CE77" s="6"/>
       <c r="CG77" s="1"/>
       <c r="CH77" s="1"/>
       <c r="CI77" s="1" t="s">
@@ -11154,8 +11551,8 @@
       <c r="CZ77" s="1"/>
     </row>
     <row r="78" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD78" s="13"/>
-      <c r="CE78" s="14"/>
+      <c r="CD78" s="7"/>
+      <c r="CE78" s="8"/>
       <c r="CG78" s="1"/>
       <c r="CH78" s="1"/>
       <c r="CI78" s="1" t="s">
@@ -11197,10 +11594,10 @@
     </row>
     <row r="79" spans="2:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="80" spans="2:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD80" s="9" t="s">
+      <c r="CD80" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="CE80" s="10"/>
+      <c r="CE80" s="4"/>
       <c r="CG80" s="1" t="s">
         <v>32</v>
       </c>
@@ -11245,10 +11642,10 @@
       <c r="CZ80" s="1"/>
     </row>
     <row r="81" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC81" s="9" t="s">
+      <c r="BC81" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="BD81" s="10"/>
+      <c r="BD81" s="4"/>
       <c r="BF81" s="1" t="s">
         <v>32</v>
       </c>
@@ -11285,8 +11682,8 @@
       <c r="BW81" s="1"/>
       <c r="BX81" s="1"/>
       <c r="BY81" s="1"/>
-      <c r="CD81" s="11"/>
-      <c r="CE81" s="12"/>
+      <c r="CD81" s="5"/>
+      <c r="CE81" s="6"/>
       <c r="CG81" s="1"/>
       <c r="CH81" s="1"/>
       <c r="CI81" s="1" t="s">
@@ -11329,8 +11726,8 @@
       <c r="CZ81" s="1"/>
     </row>
     <row r="82" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC82" s="11"/>
-      <c r="BD82" s="12"/>
+      <c r="BC82" s="5"/>
+      <c r="BD82" s="6"/>
       <c r="BF82" s="1"/>
       <c r="BG82" s="1"/>
       <c r="BH82" s="1" t="s">
@@ -11377,8 +11774,8 @@
       </c>
       <c r="BX82" s="1"/>
       <c r="BY82" s="1"/>
-      <c r="CD82" s="11"/>
-      <c r="CE82" s="12"/>
+      <c r="CD82" s="5"/>
+      <c r="CE82" s="6"/>
       <c r="CG82" s="1"/>
       <c r="CH82" s="1"/>
       <c r="CI82" s="1"/>
@@ -11401,8 +11798,8 @@
       <c r="CZ82" s="1"/>
     </row>
     <row r="83" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC83" s="11"/>
-      <c r="BD83" s="12"/>
+      <c r="BC83" s="5"/>
+      <c r="BD83" s="6"/>
       <c r="BF83" s="1"/>
       <c r="BG83" s="1"/>
       <c r="BH83" s="1" t="s">
@@ -11447,8 +11844,8 @@
       </c>
       <c r="BX83" s="1"/>
       <c r="BY83" s="1"/>
-      <c r="CD83" s="13"/>
-      <c r="CE83" s="14"/>
+      <c r="CD83" s="7"/>
+      <c r="CE83" s="8"/>
       <c r="CG83" s="1"/>
       <c r="CH83" s="1"/>
       <c r="CI83" s="1"/>
@@ -11471,8 +11868,8 @@
       <c r="CZ83" s="1"/>
     </row>
     <row r="84" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC84" s="13"/>
-      <c r="BD84" s="14"/>
+      <c r="BC84" s="7"/>
+      <c r="BD84" s="8"/>
       <c r="BF84" s="1"/>
       <c r="BG84" s="1"/>
       <c r="BH84" s="1" t="s">
@@ -11520,10 +11917,10 @@
     </row>
     <row r="86" spans="55:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="87" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC87" s="9" t="s">
+      <c r="BC87" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="BD87" s="10"/>
+      <c r="BD87" s="4"/>
       <c r="BF87" s="1" t="s">
         <v>32</v>
       </c>
@@ -11574,8 +11971,8 @@
       <c r="BY87" s="1"/>
     </row>
     <row r="88" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC88" s="11"/>
-      <c r="BD88" s="12"/>
+      <c r="BC88" s="5"/>
+      <c r="BD88" s="6"/>
       <c r="BF88" s="1"/>
       <c r="BG88" s="1"/>
       <c r="BH88" s="1" t="s">
@@ -11622,8 +12019,8 @@
       <c r="BY88" s="1"/>
     </row>
     <row r="89" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC89" s="11"/>
-      <c r="BD89" s="12"/>
+      <c r="BC89" s="5"/>
+      <c r="BD89" s="6"/>
       <c r="BF89" s="1"/>
       <c r="BG89" s="1"/>
       <c r="BH89" s="1" t="s">
@@ -11670,8 +12067,8 @@
       <c r="BY89" s="1"/>
     </row>
     <row r="90" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC90" s="13"/>
-      <c r="BD90" s="14"/>
+      <c r="BC90" s="7"/>
+      <c r="BD90" s="8"/>
       <c r="BF90" s="1"/>
       <c r="BG90" s="1"/>
       <c r="BH90" s="1" t="s">
@@ -11723,10 +12120,10 @@
     </row>
     <row r="96" spans="55:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="97" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC97" s="9" t="s">
+      <c r="BC97" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="BD97" s="10"/>
+      <c r="BD97" s="4"/>
       <c r="BF97" s="1" t="s">
         <v>32</v>
       </c>
@@ -11765,8 +12162,8 @@
       <c r="BY97" s="1"/>
     </row>
     <row r="98" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC98" s="11"/>
-      <c r="BD98" s="12"/>
+      <c r="BC98" s="5"/>
+      <c r="BD98" s="6"/>
       <c r="BF98" s="1"/>
       <c r="BG98" s="1"/>
       <c r="BH98" s="1" t="s">
@@ -11805,8 +12202,8 @@
       <c r="BY98" s="1"/>
     </row>
     <row r="99" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC99" s="11"/>
-      <c r="BD99" s="12"/>
+      <c r="BC99" s="5"/>
+      <c r="BD99" s="6"/>
       <c r="BF99" s="1"/>
       <c r="BG99" s="1"/>
       <c r="BH99" s="1" t="s">
@@ -11843,10 +12240,10 @@
       <c r="BW99" s="1"/>
       <c r="BX99" s="1"/>
       <c r="BY99" s="1"/>
-      <c r="CD99" s="9" t="s">
+      <c r="CD99" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="CE99" s="10"/>
+      <c r="CE99" s="4"/>
       <c r="CG99" s="1" t="s">
         <v>32</v>
       </c>
@@ -11885,8 +12282,8 @@
       <c r="CZ99" s="1"/>
     </row>
     <row r="100" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC100" s="13"/>
-      <c r="BD100" s="14"/>
+      <c r="BC100" s="7"/>
+      <c r="BD100" s="8"/>
       <c r="BF100" s="1"/>
       <c r="BG100" s="1"/>
       <c r="BH100" s="1" t="s">
@@ -11923,8 +12320,8 @@
       <c r="BW100" s="1"/>
       <c r="BX100" s="1"/>
       <c r="BY100" s="1"/>
-      <c r="CD100" s="11"/>
-      <c r="CE100" s="12"/>
+      <c r="CD100" s="5"/>
+      <c r="CE100" s="6"/>
       <c r="CG100" s="1"/>
       <c r="CH100" s="1"/>
       <c r="CI100" s="1" t="s">
@@ -11973,8 +12370,8 @@
       <c r="CZ100" s="1"/>
     </row>
     <row r="101" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="CD101" s="11"/>
-      <c r="CE101" s="12"/>
+      <c r="CD101" s="5"/>
+      <c r="CE101" s="6"/>
       <c r="CG101" s="1"/>
       <c r="CH101" s="1"/>
       <c r="CI101" s="1" t="s">
@@ -12027,10 +12424,10 @@
       <c r="CZ101" s="1"/>
     </row>
     <row r="102" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC102" s="9" t="s">
+      <c r="BC102" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="BD102" s="10"/>
+      <c r="BD102" s="4"/>
       <c r="BF102" s="1" t="s">
         <v>32</v>
       </c>
@@ -12069,8 +12466,8 @@
       <c r="BW102" s="1"/>
       <c r="BX102" s="1"/>
       <c r="BY102" s="1"/>
-      <c r="CD102" s="13"/>
-      <c r="CE102" s="14"/>
+      <c r="CD102" s="7"/>
+      <c r="CE102" s="8"/>
       <c r="CG102" s="1"/>
       <c r="CH102" s="1"/>
       <c r="CI102" s="1"/>
@@ -12093,8 +12490,8 @@
       <c r="CZ102" s="1"/>
     </row>
     <row r="103" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC103" s="11"/>
-      <c r="BD103" s="12"/>
+      <c r="BC103" s="5"/>
+      <c r="BD103" s="6"/>
       <c r="BF103" s="1"/>
       <c r="BG103" s="1"/>
       <c r="BH103" s="1" t="s">
@@ -12133,8 +12530,8 @@
       <c r="BY103" s="1"/>
     </row>
     <row r="104" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC104" s="11"/>
-      <c r="BD104" s="12"/>
+      <c r="BC104" s="5"/>
+      <c r="BD104" s="6"/>
       <c r="BF104" s="1"/>
       <c r="BG104" s="1"/>
       <c r="BH104" s="1" t="s">
@@ -12173,8 +12570,8 @@
       <c r="BY104" s="1"/>
     </row>
     <row r="105" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC105" s="13"/>
-      <c r="BD105" s="14"/>
+      <c r="BC105" s="7"/>
+      <c r="BD105" s="8"/>
       <c r="BF105" s="1"/>
       <c r="BG105" s="1"/>
       <c r="BH105" s="1"/>
@@ -12198,10 +12595,10 @@
     </row>
     <row r="108" spans="55:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC109" s="9" t="s">
+      <c r="BC109" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BD109" s="10"/>
+      <c r="BD109" s="4"/>
       <c r="BF109" s="1" t="s">
         <v>32</v>
       </c>
@@ -12240,8 +12637,8 @@
       <c r="BY109" s="1"/>
     </row>
     <row r="110" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC110" s="11"/>
-      <c r="BD110" s="12"/>
+      <c r="BC110" s="5"/>
+      <c r="BD110" s="6"/>
       <c r="BF110" s="1"/>
       <c r="BG110" s="1"/>
       <c r="BH110" s="1" t="s">
@@ -12292,8 +12689,8 @@
       <c r="BY110" s="1"/>
     </row>
     <row r="111" spans="55:104" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC111" s="11"/>
-      <c r="BD111" s="12"/>
+      <c r="BC111" s="5"/>
+      <c r="BD111" s="6"/>
       <c r="BF111" s="1"/>
       <c r="BG111" s="1"/>
       <c r="BH111" s="1" t="s">
@@ -12346,8 +12743,8 @@
       <c r="BY111" s="1"/>
     </row>
     <row r="112" spans="55:104" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC112" s="13"/>
-      <c r="BD112" s="14"/>
+      <c r="BC112" s="7"/>
+      <c r="BD112" s="8"/>
       <c r="BF112" s="1"/>
       <c r="BG112" s="1"/>
       <c r="BH112" s="1" t="s">
@@ -12401,10 +12798,10 @@
     </row>
     <row r="119" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC120" s="9" t="s">
+      <c r="BC120" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BD120" s="10"/>
+      <c r="BD120" s="4"/>
       <c r="BF120" s="1" t="s">
         <v>32</v>
       </c>
@@ -12443,8 +12840,8 @@
       <c r="BY120" s="1"/>
     </row>
     <row r="121" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC121" s="11"/>
-      <c r="BD121" s="12"/>
+      <c r="BC121" s="5"/>
+      <c r="BD121" s="6"/>
       <c r="BF121" s="1"/>
       <c r="BG121" s="1"/>
       <c r="BH121" s="1" t="s">
@@ -12501,8 +12898,8 @@
       </c>
     </row>
     <row r="122" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC122" s="11"/>
-      <c r="BD122" s="12"/>
+      <c r="BC122" s="5"/>
+      <c r="BD122" s="6"/>
       <c r="BF122" s="1"/>
       <c r="BG122" s="1"/>
       <c r="BH122" s="1" t="s">
@@ -12551,8 +12948,8 @@
       <c r="BY122" s="1"/>
     </row>
     <row r="123" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC123" s="13"/>
-      <c r="BD123" s="14"/>
+      <c r="BC123" s="7"/>
+      <c r="BD123" s="8"/>
       <c r="BF123" s="1"/>
       <c r="BG123" s="1"/>
       <c r="BH123" s="1" t="s">
@@ -12598,10 +12995,10 @@
     </row>
     <row r="126" spans="55:77" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="127" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC127" s="9" t="s">
+      <c r="BC127" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="BD127" s="10"/>
+      <c r="BD127" s="4"/>
       <c r="BF127" s="1" t="s">
         <v>32</v>
       </c>
@@ -12654,8 +13051,8 @@
       <c r="BY127" s="1"/>
     </row>
     <row r="128" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC128" s="11"/>
-      <c r="BD128" s="12"/>
+      <c r="BC128" s="5"/>
+      <c r="BD128" s="6"/>
       <c r="BF128" s="1"/>
       <c r="BG128" s="1"/>
       <c r="BH128" s="1" t="s">
@@ -12708,8 +13105,8 @@
       <c r="BY128" s="1"/>
     </row>
     <row r="129" spans="55:77" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="BC129" s="11"/>
-      <c r="BD129" s="12"/>
+      <c r="BC129" s="5"/>
+      <c r="BD129" s="6"/>
       <c r="BF129" s="1"/>
       <c r="BG129" s="1"/>
       <c r="BH129" s="1"/>
@@ -12732,8 +13129,8 @@
       <c r="BY129" s="1"/>
     </row>
     <row r="130" spans="55:77" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="BC130" s="13"/>
-      <c r="BD130" s="14"/>
+      <c r="BC130" s="7"/>
+      <c r="BD130" s="8"/>
       <c r="BF130" s="1"/>
       <c r="BG130" s="1"/>
       <c r="BH130" s="1"/>
@@ -12756,26 +13153,7 @@
       <c r="BY130" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="CD80:CE83"/>
-    <mergeCell ref="CD63:CE66"/>
-    <mergeCell ref="CD68:CE71"/>
-    <mergeCell ref="CD19:CE22"/>
-    <mergeCell ref="DE46:DF49"/>
-    <mergeCell ref="DE51:DF54"/>
-    <mergeCell ref="CD47:CE50"/>
-    <mergeCell ref="CD42:CE45"/>
-    <mergeCell ref="CD53:CE56"/>
-    <mergeCell ref="BC74:BD77"/>
-    <mergeCell ref="BC34:BD37"/>
-    <mergeCell ref="BC39:BD42"/>
-    <mergeCell ref="BC55:BD58"/>
-    <mergeCell ref="BC68:BD71"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="AB64:AC67"/>
-    <mergeCell ref="AB69:AC72"/>
-    <mergeCell ref="CD75:CE78"/>
-    <mergeCell ref="BC87:BD90"/>
+  <mergeCells count="35">
     <mergeCell ref="BC127:BD130"/>
     <mergeCell ref="CD28:CE31"/>
     <mergeCell ref="CD34:CE37"/>
@@ -12790,6 +13168,27 @@
     <mergeCell ref="BC109:BD112"/>
     <mergeCell ref="BC120:BD123"/>
     <mergeCell ref="CD58:CE61"/>
+    <mergeCell ref="B56:C59"/>
+    <mergeCell ref="AB64:AC67"/>
+    <mergeCell ref="AB69:AC72"/>
+    <mergeCell ref="CD75:CE78"/>
+    <mergeCell ref="BC87:BD90"/>
+    <mergeCell ref="B64:C67"/>
+    <mergeCell ref="B69:C72"/>
+    <mergeCell ref="BC74:BD77"/>
+    <mergeCell ref="BC34:BD37"/>
+    <mergeCell ref="BC39:BD42"/>
+    <mergeCell ref="BC55:BD58"/>
+    <mergeCell ref="BC68:BD71"/>
+    <mergeCell ref="CD80:CE83"/>
+    <mergeCell ref="CD63:CE66"/>
+    <mergeCell ref="CD68:CE71"/>
+    <mergeCell ref="CD19:CE22"/>
+    <mergeCell ref="DE46:DF49"/>
+    <mergeCell ref="DE51:DF54"/>
+    <mergeCell ref="CD47:CE50"/>
+    <mergeCell ref="CD42:CE45"/>
+    <mergeCell ref="CD53:CE56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
